--- a/data/trans_dic/P36$huevo-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P36$huevo-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, alimentos como huevos, queso, jamón</t>
+          <t>Población que desayuna, al menos, alimentos como huevos, queso, jamón (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,69; 5,34</t>
+          <t>1,74; 5,26</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,2; 5,72</t>
+          <t>2,08; 5,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,0; 10,01</t>
+          <t>5,19; 10,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,45</t>
+          <t>0,37; 3,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,97</t>
+          <t>0,92; 5,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,76; 9,37</t>
+          <t>3,46; 8,94</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,83</t>
+          <t>1,49; 3,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,42</t>
+          <t>1,98; 4,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,08; 8,96</t>
+          <t>5,12; 8,83</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 4,07</t>
+          <t>0,78; 4,05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,12; 6,63</t>
+          <t>2,04; 6,24</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,72; 11,4</t>
+          <t>5,81; 11,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 5,5</t>
+          <t>1,56; 5,61</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,15</t>
+          <t>0,82; 4,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,27; 9,56</t>
+          <t>4,4; 10,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,5; 4,12</t>
+          <t>1,45; 3,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,85; 4,64</t>
+          <t>1,88; 4,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,74; 9,51</t>
+          <t>5,77; 9,67</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,85</t>
+          <t>1,91; 4,92</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,73; 7,15</t>
+          <t>3,82; 7,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,95; 9,73</t>
+          <t>5,04; 9,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,78; 8,07</t>
+          <t>1,32; 7,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 5,92</t>
+          <t>1,47; 5,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,75; 10,51</t>
+          <t>2,58; 10,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 4,95</t>
+          <t>2,13; 4,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,34; 6,09</t>
+          <t>3,38; 6,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,04; 8,88</t>
+          <t>4,87; 8,71</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,46; 4,69</t>
+          <t>2,51; 4,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,48; 4,53</t>
+          <t>2,51; 4,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,21; 9,31</t>
+          <t>6,22; 9,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,59</t>
+          <t>1,29; 3,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,07; 4,78</t>
+          <t>2,14; 4,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,24; 10,13</t>
+          <t>6,49; 10,28</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,28; 3,85</t>
+          <t>2,37; 4,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,57; 4,2</t>
+          <t>2,56; 4,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,74; 9,16</t>
+          <t>6,79; 9,23</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,45; 10,2</t>
+          <t>4,28; 10,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,54; 7,52</t>
+          <t>3,64; 7,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,15; 9,34</t>
+          <t>5,27; 9,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,66</t>
+          <t>0,87; 3,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,29</t>
+          <t>0,56; 2,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,14; 7,67</t>
+          <t>4,2; 7,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,74; 5,41</t>
+          <t>2,7; 5,43</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,11; 4,04</t>
+          <t>2,06; 4,03</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,27; 7,78</t>
+          <t>5,12; 7,8</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,27; 6,79</t>
+          <t>2,25; 6,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,17; 6,87</t>
+          <t>2,45; 7,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,17; 10,09</t>
+          <t>4,28; 10,54</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,06; 2,68</t>
+          <t>1,11; 2,59</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,52; 3,73</t>
+          <t>1,53; 3,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,27; 5,81</t>
+          <t>3,21; 5,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,02</t>
+          <t>1,56; 3,1</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,94; 3,91</t>
+          <t>2,02; 3,86</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,81; 6,07</t>
+          <t>3,78; 6,17</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,01; 4,36</t>
+          <t>2,96; 4,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,47; 4,89</t>
+          <t>3,46; 4,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,56; 8,44</t>
+          <t>6,53; 8,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,64</t>
+          <t>1,63; 2,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,85; 2,91</t>
+          <t>1,82; 2,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,27; 6,91</t>
+          <t>5,35; 7,02</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,46; 3,29</t>
+          <t>2,45; 3,3</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,81; 3,7</t>
+          <t>2,82; 3,75</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,11; 7,32</t>
+          <t>6,13; 7,3</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que desayuna, al menos, alimentos como huevos, queso, jamón</t>
+          <t>Población que desayuna, al menos, alimentos como huevos, queso, jamón (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8002; 25230</t>
+          <t>8234; 24866</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9602; 24997</t>
+          <t>9110; 24005</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21448; 42931</t>
+          <t>22273; 44754</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1165; 10586</t>
+          <t>1149; 10907</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2922; 15558</t>
+          <t>2889; 15891</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13034; 32507</t>
+          <t>12013; 31017</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11074; 29860</t>
+          <t>11578; 30492</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14021; 33192</t>
+          <t>14893; 33954</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>39410; 69506</t>
+          <t>39763; 68527</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2967; 14847</t>
+          <t>2856; 14799</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8839; 27626</t>
+          <t>8489; 25990</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21569; 43018</t>
+          <t>21908; 44236</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5812; 20378</t>
+          <t>5786; 20797</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2778; 14016</t>
+          <t>2782; 14527</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15844; 35487</t>
+          <t>16344; 37166</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11042; 30317</t>
+          <t>10702; 29387</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13943; 35029</t>
+          <t>14173; 35116</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>42977; 71189</t>
+          <t>43202; 72363</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>9892; 26196</t>
+          <t>10331; 26562</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>23378; 44848</t>
+          <t>23965; 45308</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>25784; 50694</t>
+          <t>26243; 49964</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2990; 13538</t>
+          <t>2216; 13157</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3974; 15394</t>
+          <t>3832; 15407</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4561; 17460</t>
+          <t>4288; 16717</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14836; 35046</t>
+          <t>15098; 34439</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>29673; 54073</t>
+          <t>30032; 53653</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>34611; 60968</t>
+          <t>33486; 59830</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>30442; 57946</t>
+          <t>31040; 58240</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28736; 52466</t>
+          <t>29040; 52880</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>71375; 106971</t>
+          <t>71397; 107009</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9334; 25594</t>
+          <t>9180; 25563</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>15846; 36574</t>
+          <t>16371; 37993</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>51558; 83636</t>
+          <t>53579; 84892</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>44481; 75101</t>
+          <t>46255; 77920</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>49446; 80813</t>
+          <t>49159; 81189</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>133104; 180832</t>
+          <t>134022; 182265</t>
         </is>
       </c>
     </row>
@@ -2291,47 +2291,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15610; 35743</t>
+          <t>15017; 36640</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>18027; 38322</t>
+          <t>18541; 38250</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31886; 57786</t>
+          <t>32611; 58702</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5235; 20766</t>
+          <t>4918; 20261</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4818; 17357</t>
+          <t>4210; 16039</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>30582; 56597</t>
+          <t>31033; 57154</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25112; 49636</t>
+          <t>24801; 49784</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>26786; 51222</t>
+          <t>26074; 51089</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>71563; 105561</t>
+          <t>69456; 105857</t>
         </is>
       </c>
     </row>
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6759; 20253</t>
+          <t>6712; 20069</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5781; 18328</t>
+          <t>6526; 19147</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11980; 28965</t>
+          <t>12300; 30266</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13264; 33459</t>
+          <t>13814; 32365</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16892; 41381</t>
+          <t>17018; 39145</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>35264; 62695</t>
+          <t>34618; 63077</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23603; 46745</t>
+          <t>24154; 48001</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>26694; 53756</t>
+          <t>27745; 53096</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>52026; 82944</t>
+          <t>51641; 84380</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>98136; 142157</t>
+          <t>96701; 143797</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>118635; 167167</t>
+          <t>118174; 165399</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>221943; 285569</t>
+          <t>220950; 280319</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>55908; 89228</t>
+          <t>55032; 88249</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>65431; 103266</t>
+          <t>64624; 104620</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>185936; 243721</t>
+          <t>188795; 247689</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>163097; 218701</t>
+          <t>162459; 218999</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>195395; 257682</t>
+          <t>196575; 260827</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>422334; 505584</t>
+          <t>423506; 504760</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36$huevo-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P36$huevo-Clase-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,74; 5,26</t>
+          <t>1,73; 5,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,08; 5,49</t>
+          <t>2,17; 5,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5,19; 10,43</t>
+          <t>4,94; 10,36</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,56</t>
+          <t>0,37; 3,18</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 5,07</t>
+          <t>0,92; 4,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,46; 8,94</t>
+          <t>3,9; 9,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,91</t>
+          <t>1,44; 4,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,52</t>
+          <t>1,89; 4,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5,12; 8,83</t>
+          <t>4,97; 8,79</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,78; 4,05</t>
+          <t>0,78; 4,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,04; 6,24</t>
+          <t>2,16; 6,41</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,81; 11,73</t>
+          <t>5,59; 11,51</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,56; 5,61</t>
+          <t>1,45; 5,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,3</t>
+          <t>0,81; 4,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,4; 10,01</t>
+          <t>4,58; 10,12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 3,99</t>
+          <t>1,44; 4,03</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,65</t>
+          <t>1,82; 4,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>5,77; 9,67</t>
+          <t>5,8; 9,71</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,92</t>
+          <t>1,69; 5,12</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3,82; 7,22</t>
+          <t>3,72; 7,38</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,04; 9,59</t>
+          <t>5,19; 9,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 7,84</t>
+          <t>1,36; 8,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 5,92</t>
+          <t>1,23; 5,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,58; 10,06</t>
+          <t>2,99; 10,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,13; 4,86</t>
+          <t>2,07; 4,78</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,38; 6,04</t>
+          <t>3,42; 6,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4,87; 8,71</t>
+          <t>4,99; 8,73</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,51; 4,71</t>
+          <t>2,48; 4,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,51; 4,57</t>
+          <t>2,44; 4,68</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,22; 9,32</t>
+          <t>6,12; 9,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,58</t>
+          <t>1,34; 3,48</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,14; 4,97</t>
+          <t>2,11; 4,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,49; 10,28</t>
+          <t>6,47; 10,43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,37; 4,0</t>
+          <t>2,31; 3,85</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,56; 4,22</t>
+          <t>2,54; 4,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,79; 9,23</t>
+          <t>6,75; 9,19</t>
         </is>
       </c>
     </row>
@@ -1118,54 +1118,54 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,28; 10,45</t>
+          <t>4,21; 10,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,64; 7,5</t>
+          <t>3,62; 7,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,27; 9,48</t>
+          <t>5,33; 9,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,57</t>
+          <t>0,97; 3,8</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,56; 2,11</t>
+          <t>0,65; 2,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,2; 7,74</t>
+          <t>4,19; 7,86</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,7; 5,43</t>
+          <t>2,6; 5,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,06; 4,03</t>
+          <t>2,03; 3,99</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5,12; 7,8</t>
+          <t>5,14; 7,98</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,25; 6,73</t>
+          <t>2,25; 6,84</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,45; 7,17</t>
+          <t>2,2; 7,24</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4,28; 10,54</t>
+          <t>4,04; 9,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,59</t>
+          <t>1,13; 2,52</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,53</t>
+          <t>1,6; 3,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,21; 5,84</t>
+          <t>3,29; 5,75</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,56; 3,1</t>
+          <t>1,58; 3,04</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,02; 3,86</t>
+          <t>2,0; 3,83</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,78; 6,17</t>
+          <t>3,81; 6,11</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,96; 4,41</t>
+          <t>3,01; 4,36</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,46; 4,84</t>
+          <t>3,56; 4,94</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,53; 8,29</t>
+          <t>6,58; 8,45</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,63; 2,62</t>
+          <t>1,63; 2,68</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,82; 2,95</t>
+          <t>1,87; 2,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,35; 7,02</t>
+          <t>5,24; 6,87</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,45; 3,3</t>
+          <t>2,46; 3,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,82; 3,75</t>
+          <t>2,82; 3,68</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>6,13; 7,3</t>
+          <t>6,14; 7,36</t>
         </is>
       </c>
     </row>
@@ -1639,47 +1639,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>8234; 24866</t>
+          <t>8179; 24250</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>9110; 24005</t>
+          <t>9506; 24348</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22273; 44754</t>
+          <t>21185; 44455</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1149; 10907</t>
+          <t>1148; 9754</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>2889; 15891</t>
+          <t>2880; 15498</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12013; 31017</t>
+          <t>13547; 32686</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11578; 30492</t>
+          <t>11199; 31611</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>14893; 33954</t>
+          <t>14207; 33695</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>39763; 68527</t>
+          <t>38567; 68190</t>
         </is>
       </c>
     </row>
@@ -1802,47 +1802,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2856; 14799</t>
+          <t>2865; 15153</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8489; 25990</t>
+          <t>9008; 26714</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21908; 44236</t>
+          <t>21105; 43414</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5786; 20797</t>
+          <t>5388; 20268</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2782; 14527</t>
+          <t>2735; 14615</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16344; 37166</t>
+          <t>16983; 37563</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10702; 29387</t>
+          <t>10612; 29626</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14173; 35116</t>
+          <t>13747; 35102</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>43202; 72363</t>
+          <t>43441; 72683</t>
         </is>
       </c>
     </row>
@@ -1965,47 +1965,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10331; 26562</t>
+          <t>9135; 27680</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>23965; 45308</t>
+          <t>23342; 46303</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26243; 49964</t>
+          <t>27008; 51240</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2216; 13157</t>
+          <t>2277; 13595</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3832; 15407</t>
+          <t>3212; 14700</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4288; 16717</t>
+          <t>4972; 17692</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15098; 34439</t>
+          <t>14691; 33859</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>30032; 53653</t>
+          <t>30323; 56026</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>33486; 59830</t>
+          <t>34276; 59958</t>
         </is>
       </c>
     </row>
@@ -2128,47 +2128,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>31040; 58240</t>
+          <t>30602; 57901</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29040; 52880</t>
+          <t>28255; 54142</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>71397; 107009</t>
+          <t>70272; 106927</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9180; 25563</t>
+          <t>9585; 24828</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16371; 37993</t>
+          <t>16132; 36566</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>53579; 84892</t>
+          <t>53445; 86172</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>46255; 77920</t>
+          <t>44999; 74973</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>49159; 81189</t>
+          <t>48740; 81024</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>134022; 182265</t>
+          <t>133341; 181404</t>
         </is>
       </c>
     </row>
@@ -2291,54 +2291,54 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>15017; 36640</t>
+          <t>14748; 35445</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>18541; 38250</t>
+          <t>18464; 38645</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>32611; 58702</t>
+          <t>33008; 58678</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4918; 20261</t>
+          <t>5488; 21565</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4210; 16039</t>
+          <t>4929; 18363</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>31033; 57154</t>
+          <t>30940; 58024</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>24801; 49784</t>
+          <t>23811; 50672</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>26074; 51089</t>
+          <t>25713; 50626</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>69456; 105857</t>
+          <t>69825; 108239</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2454,47 +2454,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6712; 20069</t>
+          <t>6697; 20389</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>6526; 19147</t>
+          <t>5866; 19329</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>12300; 30266</t>
+          <t>11596; 28621</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13814; 32365</t>
+          <t>14113; 31486</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>17018; 39145</t>
+          <t>17775; 40200</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>34618; 63077</t>
+          <t>35496; 62128</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>24154; 48001</t>
+          <t>24513; 47032</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>27745; 53096</t>
+          <t>27506; 52689</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>51641; 84380</t>
+          <t>52037; 83527</t>
         </is>
       </c>
     </row>
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>96701; 143797</t>
+          <t>98237; 142224</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>118174; 165399</t>
+          <t>121754; 168616</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>220950; 280319</t>
+          <t>222592; 285901</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>55032; 88249</t>
+          <t>55115; 90423</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>64624; 104620</t>
+          <t>66132; 102931</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>188795; 247689</t>
+          <t>184737; 242297</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>162459; 218999</t>
+          <t>163389; 220056</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>196575; 260827</t>
+          <t>196053; 255906</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>423506; 504760</t>
+          <t>424248; 508383</t>
         </is>
       </c>
     </row>
